--- a/reports/tables/SHAP_Feature_Importance_FirstVisit.xlsx
+++ b/reports/tables/SHAP_Feature_Importance_FirstVisit.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.419154015312979</v>
+        <v>0.1729599853646095</v>
       </c>
     </row>
     <row r="3">
@@ -459,11 +459,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Female age (years)</t>
+          <t>Total female pathology score</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4026073318385659</v>
+        <v>0.1166534573602819</v>
       </c>
     </row>
     <row r="4">
@@ -472,11 +472,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PRL Baseline</t>
+          <t>Female age (years)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3904656659138027</v>
+        <v>0.08959773415991337</v>
       </c>
     </row>
     <row r="5">
@@ -485,11 +485,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Total female pathology score</t>
+          <t>Gynecological surgical history</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3480712998175671</v>
+        <v>0.06867814987222656</v>
       </c>
     </row>
     <row r="6">
@@ -498,11 +498,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Age FSH Interaction</t>
+          <t>Menstrual cycle length (days)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3151653952567166</v>
+        <v>0.05112316435252648</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3065848600782688</v>
+        <v>0.03522797340130026</v>
       </c>
     </row>
     <row r="8">
@@ -524,11 +524,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Menstrual cycle length (days)</t>
+          <t>FSH Baseline</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.2797233124226167</v>
+        <v>0.02815649002299741</v>
       </c>
     </row>
     <row r="9">
@@ -537,11 +537,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Initial semen volume (mL)</t>
+          <t>Initial TPMSC (million)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.2787853565595635</v>
+        <v>0.02408551850630022</v>
       </c>
     </row>
     <row r="10">
@@ -550,11 +550,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prior gynecologic surgery</t>
+          <t>Infertility duration (months)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.2448462254860884</v>
+        <v>0.02201728196762079</v>
       </c>
     </row>
     <row r="11">
@@ -563,11 +563,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BMI (kg/m²)</t>
+          <t>Alcohol</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.2352043776707737</v>
+        <v>0.02196619289671178</v>
       </c>
     </row>
     <row r="12">
@@ -576,11 +576,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E2 Baseline</t>
+          <t>BMI x infertility type</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2195925624334582</v>
+        <v>0.02182553533194177</v>
       </c>
     </row>
     <row r="13">
@@ -589,11 +589,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Age Male</t>
+          <t>First Normal Morpho</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2057513111917904</v>
+        <v>0.0204513179549111</v>
       </c>
     </row>
     <row r="14">
@@ -602,11 +602,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Infertility duration (months)</t>
+          <t>Number Of Alive Children</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2032446185772432</v>
+        <v>0.0177044315051991</v>
       </c>
     </row>
     <row r="15">
@@ -615,11 +615,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FSH Baseline</t>
+          <t>Initial progressive motility (%)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1929383467867131</v>
+        <v>0.01665019018329818</v>
       </c>
     </row>
     <row r="16">
@@ -628,11 +628,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>First Normal Morpho</t>
+          <t>Dysmenorrhea</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1748094624015065</v>
+        <v>0.01436212364551096</v>
       </c>
     </row>
     <row r="17">
@@ -641,11 +641,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LH Baseline</t>
+          <t>Age–FSH interaction</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.1712381982575799</v>
+        <v>0.01420963958907844</v>
       </c>
     </row>
     <row r="18">
@@ -654,11 +654,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dysmenorrhea</t>
+          <t>Initial semen volume (mL)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1599934392743879</v>
+        <v>0.01405357951737299</v>
       </c>
     </row>
     <row r="19">
@@ -667,11 +667,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Initial TPMSC (million)</t>
+          <t>E2 Baseline</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1590963435893545</v>
+        <v>0.01298620417862136</v>
       </c>
     </row>
     <row r="20">
@@ -680,11 +680,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alcohol</t>
+          <t>Number Of Miscarriages</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1497673607825377</v>
+        <v>0.01126407222499178</v>
       </c>
     </row>
     <row r="21">
@@ -693,11 +693,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Initial progressive motility (%)</t>
+          <t>Smoke</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1481298340030527</v>
+        <v>0.01089911336726848</v>
       </c>
     </row>
     <row r="22">
@@ -706,11 +706,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>First Motile</t>
+          <t>PRL Baseline</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1320028029788444</v>
+        <v>0.009611206631145227</v>
       </c>
     </row>
     <row r="23">
@@ -719,11 +719,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BMI x infertility type</t>
+          <t>First Motile</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1197980369731844</v>
+        <v>0.009189771754726192</v>
       </c>
     </row>
     <row r="24">
@@ -732,11 +732,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Menstrual Duration Days</t>
+          <t>LH Baseline</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1048743944319001</v>
+        <v>0.008918666355418126</v>
       </c>
     </row>
     <row r="25">
@@ -745,11 +745,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Number Of Alive Children</t>
+          <t>BMI (kg/m²)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.09421221433508731</v>
+        <v>0.008053132542657798</v>
       </c>
     </row>
     <row r="26">
@@ -758,11 +758,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Smoke</t>
+          <t>Age Male</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.06636341473847597</v>
+        <v>0.005469309534507148</v>
       </c>
     </row>
     <row r="27">
@@ -771,11 +771,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pregnancy History</t>
+          <t>Multisystem Factors</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.04482497473358785</v>
+        <v>0.004975649187452807</v>
       </c>
     </row>
     <row r="28">
@@ -784,11 +784,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Number Of Miscarriages</t>
+          <t>Pregnancy History</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.04230309407212503</v>
+        <v>0.004817580735743689</v>
       </c>
     </row>
     <row r="29">
@@ -797,11 +797,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tubal factor</t>
+          <t>Menstrual Duration Days</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.03884562180069204</v>
+        <v>0.003822955733121368</v>
       </c>
     </row>
     <row r="30">
@@ -810,11 +810,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ovarian Factors</t>
+          <t>Tubal factor</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.03312106631836855</v>
+        <v>0.003201135437226452</v>
       </c>
     </row>
     <row r="31">
@@ -823,11 +823,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ovulatory factor</t>
+          <t>Infertility type</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.03087995051842203</v>
+        <v>0.002884689491768953</v>
       </c>
     </row>
     <row r="32">
@@ -836,11 +836,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Infertility type</t>
+          <t>Ovulatory factor</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.02370518542607995</v>
+        <v>0.00277104742868595</v>
       </c>
     </row>
     <row r="33">
@@ -849,11 +849,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Endometriosis</t>
+          <t>Ovarian Factors</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01488810535965998</v>
+        <v>0.002580293712207373</v>
       </c>
     </row>
     <row r="34">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01482344108595441</v>
+        <v>0.002250069804204015</v>
       </c>
     </row>
     <row r="35">
@@ -875,11 +875,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cervical Factors</t>
+          <t>Endometriosis</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.0002211467384994929</v>
       </c>
     </row>
     <row r="36">
@@ -888,11 +888,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Multisystem Factors</t>
+          <t>Cervical Factors</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.0001937680645044376</v>
       </c>
     </row>
   </sheetData>
